--- a/data/trending_integrated_20261026_09.xlsx
+++ b/data/trending_integrated_20261026_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:Z5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1283000</v>
+        <v>1309000</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+0.47%</t>
+          <t>'+2.51%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.08</v>
       </c>
       <c r="E2" t="n">
-        <v>583</v>
+        <v>650</v>
       </c>
       <c r="F2" t="n">
-        <v>351</v>
+        <v>385</v>
       </c>
       <c r="G2" t="n">
-        <v>2549</v>
+        <v>2629</v>
       </c>
       <c r="H2" t="n">
         <v>48.69</v>
@@ -601,7 +601,7 @@
         <v>1279000</v>
       </c>
       <c r="L2" t="n">
-        <v>1291000</v>
+        <v>1315000</v>
       </c>
       <c r="M2" t="n">
         <v>1272000</v>
@@ -610,7 +610,7 @@
         <v>48.77</v>
       </c>
       <c r="O2" t="n">
-        <v>158375861500</v>
+        <v>507287434500</v>
       </c>
       <c r="P2" t="n">
         <v>2987000</v>
@@ -649,6 +649,282 @@
       <c r="Z2" t="inlineStr">
         <is>
           <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>214750</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>'-0.35%</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E3" t="n">
+        <v>545</v>
+      </c>
+      <c r="F3" t="n">
+        <v>340</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1570</v>
+      </c>
+      <c r="H3" t="n">
+        <v>46.11</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>215500</v>
+      </c>
+      <c r="K3" t="n">
+        <v>213500</v>
+      </c>
+      <c r="L3" t="n">
+        <v>216000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>211500</v>
+      </c>
+      <c r="N3" t="n">
+        <v>46.13</v>
+      </c>
+      <c r="O3" t="n">
+        <v>387036641750</v>
+      </c>
+      <c r="P3" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>94500</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>3분기 영업이익 호재에도 불구하고 정치적 리스크와 증시 시스템 문제 언급. 미국 반도체 시간 외 폭등과 나스닥 선물 급등은 호재로 작용 가능성. 그러나 전반적으로 하락 및 폭락에 대한 우려가 공존.</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>['영업이익', '반도체', '시스템']</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>58800</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>'-1.01%</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F4" t="n">
+        <v>54</v>
+      </c>
+      <c r="G4" t="n">
+        <v>180</v>
+      </c>
+      <c r="H4" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>59400</v>
+      </c>
+      <c r="K4" t="n">
+        <v>58300</v>
+      </c>
+      <c r="L4" t="n">
+        <v>59000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>57600</v>
+      </c>
+      <c r="N4" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="O4" t="n">
+        <v>12447067250</v>
+      </c>
+      <c r="P4" t="n">
+        <v>139200</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>57000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>현재 가격이 저점이라는 의견과 함께 공포 구간 진입 언급. 적정 주가에 대한 다양한 의견 제시. 반도체 시장 하락 시 원전으로의 수혜 기대와 달리 증시 전반의 하락세에 대한 우려.</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>['적정주가', '원전', '증시']</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>빅텍</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3365</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>'-11.68%</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>102</v>
+      </c>
+      <c r="F5" t="n">
+        <v>67</v>
+      </c>
+      <c r="G5" t="n">
+        <v>156</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>3810</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3250</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3405</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3215</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>6534240334</v>
+      </c>
+      <c r="P5" t="n">
+        <v>7050</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2500</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>북한의 군사회담 제안에 대한 자주포 도발 및 미-이란 전면전 위기 고조 관련 내용. 지정학적 리스크 부각으로 인한 급등 가능성 언급. 일부는 하락 및 거품 제거를 주장.</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>['자주포', '지정학적', '전면전']</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>065450</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261026_09.xlsx
+++ b/data/trending_integrated_20261026_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,83 +563,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1309000</v>
+        <v>14400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+2.51%</t>
+          <t>'+27.43%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.08</v>
+        <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>650</v>
+        <v>45</v>
       </c>
       <c r="F2" t="n">
-        <v>385</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>2629</v>
+        <v>105</v>
       </c>
       <c r="H2" t="n">
-        <v>48.69</v>
+        <v>7.36</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1277000</v>
+        <v>11300</v>
       </c>
       <c r="K2" t="n">
-        <v>1279000</v>
+        <v>12450</v>
       </c>
       <c r="L2" t="n">
-        <v>1315000</v>
+        <v>14500</v>
       </c>
       <c r="M2" t="n">
-        <v>1272000</v>
+        <v>12150</v>
       </c>
       <c r="N2" t="n">
-        <v>48.77</v>
+        <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>507287434500</v>
+        <v>20689636125</v>
       </c>
       <c r="P2" t="n">
-        <v>2987000</v>
+        <v>49800</v>
       </c>
       <c r="Q2" t="n">
-        <v>501000</v>
+        <v>8180</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>53000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>SK하이닉스, 일본 키옥시아 지분 매각 차익 16조원을 활용한 특별배당 추진 공시. 주당 2만3000원 안팎 배당 예상.</t>
+          <t>루닛, 글로벌 AI 신약 밸류체인 합류 및 빅파마 3곳과 후기 임상 진입 소식. 루닛스코프 가치 5000억 및 내년 매출 500억 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['특별배당', '키옥시아', '지분차익']</t>
+          <t>['AI 신약', '루닛스코프', '후기 임상']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>214750</v>
+        <v>1300000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'-0.35%</t>
+          <t>'+1.80%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.02</v>
+        <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>545</v>
+        <v>716</v>
       </c>
       <c r="F3" t="n">
-        <v>340</v>
+        <v>426</v>
       </c>
       <c r="G3" t="n">
-        <v>1570</v>
+        <v>2710</v>
       </c>
       <c r="H3" t="n">
-        <v>46.11</v>
+        <v>48.69</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>215500</v>
+        <v>1277000</v>
       </c>
       <c r="K3" t="n">
-        <v>213500</v>
+        <v>1279000</v>
       </c>
       <c r="L3" t="n">
-        <v>216000</v>
+        <v>1315000</v>
       </c>
       <c r="M3" t="n">
-        <v>211500</v>
+        <v>1272000</v>
       </c>
       <c r="N3" t="n">
-        <v>46.13</v>
+        <v>48.77</v>
       </c>
       <c r="O3" t="n">
-        <v>387036641750</v>
+        <v>653377278000</v>
       </c>
       <c r="P3" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q3" t="n">
-        <v>94500</v>
+        <v>501000</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>3분기 영업이익 호재에도 불구하고 정치적 리스크와 증시 시스템 문제 언급. 미국 반도체 시간 외 폭등과 나스닥 선물 급등은 호재로 작용 가능성. 그러나 전반적으로 하락 및 폭락에 대한 우려가 공존.</t>
+          <t>SK하이닉스, 일본 키옥시아 지분 차익 16조원 특별배당 추진 관련 단독 뉴스 확인. 주당 2만3000원 안팎 배당 예상 및 2026년 영익 262조원, 내년 403조원 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['영업이익', '반도체', '시스템']</t>
+          <t>['특별배당', '키옥시아 지분', '실적 전망']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>58800</v>
+        <v>59400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'-1.01%</t>
+          <t>'-0.67%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.02</v>
+        <v>1.49</v>
       </c>
       <c r="E4" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="G4" t="n">
-        <v>180</v>
+        <v>238</v>
       </c>
       <c r="H4" t="n">
-        <v>22.23</v>
+        <v>40.39</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
+        <v>59800</v>
+      </c>
+      <c r="K4" t="n">
         <v>59400</v>
       </c>
-      <c r="K4" t="n">
-        <v>58300</v>
-      </c>
       <c r="L4" t="n">
-        <v>59000</v>
+        <v>60200</v>
       </c>
       <c r="M4" t="n">
-        <v>57600</v>
+        <v>57800</v>
       </c>
       <c r="N4" t="n">
-        <v>22.25</v>
+        <v>38.9</v>
       </c>
       <c r="O4" t="n">
-        <v>12447067250</v>
+        <v>70201055300</v>
       </c>
       <c r="P4" t="n">
-        <v>139200</v>
+        <v>67300</v>
       </c>
       <c r="Q4" t="n">
-        <v>57000</v>
+        <v>23150</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>현재 가격이 저점이라는 의견과 함께 공포 구간 진입 언급. 적정 주가에 대한 다양한 의견 제시. 반도체 시장 하락 시 원전으로의 수혜 기대와 달리 증시 전반의 하락세에 대한 우려.</t>
+          <t>대형 수주 공시 임박 및 중동 전쟁 장기화 가능성에 따른 기대감. 자사주 매수 및 외인 매수세 유입으로 인한 관성적 전고점 돌파 추세 분석.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['적정주가', '원전', '증시']</t>
+          <t>['대형 수주', '자사주 매수', '중동 전쟁']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,97 +832,281 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>빅텍</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3365</v>
+        <v>214000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-11.68%</t>
+          <t>'-0.70%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>102</v>
+        <v>586</v>
       </c>
       <c r="F5" t="n">
-        <v>67</v>
+        <v>360</v>
       </c>
       <c r="G5" t="n">
-        <v>156</v>
+        <v>1636</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>46.11</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3810</v>
+        <v>215500</v>
       </c>
       <c r="K5" t="n">
-        <v>3250</v>
+        <v>213500</v>
       </c>
       <c r="L5" t="n">
-        <v>3405</v>
+        <v>216000</v>
       </c>
       <c r="M5" t="n">
-        <v>3215</v>
+        <v>211500</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>46.13</v>
       </c>
       <c r="O5" t="n">
-        <v>6534240334</v>
+        <v>504288842250</v>
       </c>
       <c r="P5" t="n">
-        <v>7050</v>
+        <v>374500</v>
       </c>
       <c r="Q5" t="n">
-        <v>2500</v>
+        <v>94500</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-244000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>북한의 군사회담 제안에 대한 자주포 도발 및 미-이란 전면전 위기 고조 관련 내용. 지정학적 리스크 부각으로 인한 급등 가능성 언급. 일부는 하락 및 거품 제거를 주장.</t>
+          <t>3분기 영업이익 호재에도 불구하고 정치적 리스크와 증시 시스템 문제 언급. 미국 반도체 시간 외 폭등과 나스닥 선물 급등은 호재로 작용 가능성. 그러나 전반적으로 하락 및 폭락에 대한 우려가 공존.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['자주포', '지정학적', '전면전']</t>
+          <t>['영업이익', '반도체', '시스템']</t>
         </is>
       </c>
       <c r="X5" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>58900</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>'-0.84%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E6" t="n">
+        <v>63</v>
+      </c>
+      <c r="F6" t="n">
+        <v>56</v>
+      </c>
+      <c r="G6" t="n">
+        <v>197</v>
+      </c>
+      <c r="H6" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>59400</v>
+      </c>
+      <c r="K6" t="n">
+        <v>58300</v>
+      </c>
+      <c r="L6" t="n">
+        <v>59000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>57600</v>
+      </c>
+      <c r="N6" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="O6" t="n">
+        <v>16316955500</v>
+      </c>
+      <c r="P6" t="n">
+        <v>139200</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>57000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>37000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>두산에너빌리티, 신용 물량 및 반도체 시장 침체 영향으로 인한 하락세. 공포선 도달 및 52주 최저가 근접 상황.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['신용 물량', '반도체 침체', '52주 최저가']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>빅텍</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3535</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>'-7.22%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>121</v>
+      </c>
+      <c r="F7" t="n">
+        <v>78</v>
+      </c>
+      <c r="G7" t="n">
+        <v>169</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>3810</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3250</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3545</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3215</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>9198464666</v>
+      </c>
+      <c r="P7" t="n">
+        <v>7050</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2500</v>
+      </c>
+      <c r="R7" t="n">
+        <v>141000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>북한의 자주포 남쪽 조준 및 미-이란 전면전 위기 고조와 관련된 군사적 긴장감 속에서 일부 기대감 형성. 그러나 변동성이 큰 양상.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['군사적 긴장', '자주포', '전면전 위기']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
         <v>5</v>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>065450</t>
         </is>

--- a/data/trending_integrated_20261026_09.xlsx
+++ b/data/trending_integrated_20261026_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14400</v>
+        <v>14440</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+27.43%</t>
+          <t>'+27.79%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="F2" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="G2" t="n">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -601,7 +601,7 @@
         <v>12450</v>
       </c>
       <c r="L2" t="n">
-        <v>14500</v>
+        <v>14690</v>
       </c>
       <c r="M2" t="n">
         <v>12150</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>20689636125</v>
+        <v>39027837240</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>루닛, 글로벌 AI 신약 밸류체인 합류 및 빅파마 3곳과 후기 임상 진입 소식. 루닛스코프 가치 5000억 및 내년 매출 500억 전망.</t>
+          <t>글로벌 AI 신약 밸류체인 합류, 빅파마와 후기 임상 진입, 美 서밋과 항암 신약 개발 협력 등 다수 호재 기반 급등.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI 신약', '루닛스코프', '후기 임상']</t>
+          <t>['AI 신약', '후기 임상', '항암 신약']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>진양산업</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1300000</v>
+        <v>5800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+1.80%</t>
+          <t>'+5.65%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.08</v>
+        <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>716</v>
+        <v>40</v>
       </c>
       <c r="F3" t="n">
-        <v>426</v>
+        <v>19</v>
       </c>
       <c r="G3" t="n">
-        <v>2710</v>
+        <v>61</v>
       </c>
       <c r="H3" t="n">
-        <v>48.69</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1277000</v>
+        <v>5490</v>
       </c>
       <c r="K3" t="n">
-        <v>1279000</v>
+        <v>6250</v>
       </c>
       <c r="L3" t="n">
-        <v>1315000</v>
+        <v>6340</v>
       </c>
       <c r="M3" t="n">
-        <v>1272000</v>
+        <v>5650</v>
       </c>
       <c r="N3" t="n">
-        <v>48.77</v>
+        <v>2.67</v>
       </c>
       <c r="O3" t="n">
-        <v>653377278000</v>
+        <v>12420970510</v>
       </c>
       <c r="P3" t="n">
-        <v>2987000</v>
+        <v>7400</v>
       </c>
       <c r="Q3" t="n">
-        <v>501000</v>
+        <v>3660</v>
       </c>
       <c r="R3" t="n">
-        <v>44000</v>
+        <v>-48000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>SK하이닉스, 일본 키옥시아 지분 차익 16조원 특별배당 추진 관련 단독 뉴스 확인. 주당 2만3000원 안팎 배당 예상 및 2026년 영익 262조원, 내년 403조원 전망.</t>
+          <t>정치 테마 관련 부정적 언급 및 급락 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['특별배당', '키옥시아 지분', '실적 전망']</t>
+          <t>['정치 테마', '급락', '사기']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>003780</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59400</v>
+        <v>1293000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'-0.67%</t>
+          <t>'+1.25%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.49</v>
+        <v>-0.08</v>
       </c>
       <c r="E4" t="n">
-        <v>48</v>
+        <v>777</v>
       </c>
       <c r="F4" t="n">
-        <v>38</v>
+        <v>453</v>
       </c>
       <c r="G4" t="n">
-        <v>238</v>
+        <v>2777</v>
       </c>
       <c r="H4" t="n">
-        <v>40.39</v>
+        <v>48.69</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>59800</v>
+        <v>1277000</v>
       </c>
       <c r="K4" t="n">
-        <v>59400</v>
+        <v>1279000</v>
       </c>
       <c r="L4" t="n">
-        <v>60200</v>
+        <v>1315000</v>
       </c>
       <c r="M4" t="n">
-        <v>57800</v>
+        <v>1272000</v>
       </c>
       <c r="N4" t="n">
-        <v>38.9</v>
+        <v>48.77</v>
       </c>
       <c r="O4" t="n">
-        <v>70201055300</v>
+        <v>760053997500</v>
       </c>
       <c r="P4" t="n">
-        <v>67300</v>
+        <v>2987000</v>
       </c>
       <c r="Q4" t="n">
-        <v>23150</v>
+        <v>501000</v>
       </c>
       <c r="R4" t="n">
-        <v>85000</v>
+        <v>44000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>대형 수주 공시 임박 및 중동 전쟁 장기화 가능성에 따른 기대감. 자사주 매수 및 외인 매수세 유입으로 인한 관성적 전고점 돌파 추세 분석.</t>
+          <t>日 키옥시아 지분 차익 16조원 특별배당 추진 뉴스 기반 강한 상승 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['대형 수주', '자사주 매수', '중동 전쟁']</t>
+          <t>['특별배당', '키옥시아', '지분 차익']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>214000</v>
+        <v>214250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-0.70%</t>
+          <t>'-0.58%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>586</v>
+        <v>641</v>
       </c>
       <c r="F5" t="n">
-        <v>360</v>
+        <v>393</v>
       </c>
       <c r="G5" t="n">
-        <v>1636</v>
+        <v>1684</v>
       </c>
       <c r="H5" t="n">
         <v>46.11</v>
@@ -886,7 +886,7 @@
         <v>46.13</v>
       </c>
       <c r="O5" t="n">
-        <v>504288842250</v>
+        <v>610813360000</v>
       </c>
       <c r="P5" t="n">
         <v>374500</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>3분기 영업이익 호재에도 불구하고 정치적 리스크와 증시 시스템 문제 언급. 미국 반도체 시간 외 폭등과 나스닥 선물 급등은 호재로 작용 가능성. 그러나 전반적으로 하락 및 폭락에 대한 우려가 공존.</t>
+          <t>정치적 요인 언급, 3분기 영업이익 107조 호재 언급 후 폭락 및 시스템 문제 지적.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['영업이익', '반도체', '시스템']</t>
+          <t>['영업이익', '정치', '시스템']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,11 +931,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58900</v>
+        <v>59300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -943,19 +943,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.02</v>
+        <v>1.49</v>
       </c>
       <c r="E6" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="F6" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="G6" t="n">
-        <v>197</v>
+        <v>268</v>
       </c>
       <c r="H6" t="n">
-        <v>22.23</v>
+        <v>40.39</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
+        <v>59800</v>
+      </c>
+      <c r="K6" t="n">
         <v>59400</v>
       </c>
-      <c r="K6" t="n">
-        <v>58300</v>
-      </c>
       <c r="L6" t="n">
-        <v>59000</v>
+        <v>60200</v>
       </c>
       <c r="M6" t="n">
-        <v>57600</v>
+        <v>57800</v>
       </c>
       <c r="N6" t="n">
-        <v>22.25</v>
+        <v>38.9</v>
       </c>
       <c r="O6" t="n">
-        <v>16316955500</v>
+        <v>80859314650</v>
       </c>
       <c r="P6" t="n">
-        <v>139200</v>
+        <v>67300</v>
       </c>
       <c r="Q6" t="n">
-        <v>57000</v>
+        <v>23150</v>
       </c>
       <c r="R6" t="n">
-        <v>37000</v>
+        <v>85000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>두산에너빌리티, 신용 물량 및 반도체 시장 침체 영향으로 인한 하락세. 공포선 도달 및 52주 최저가 근접 상황.</t>
+          <t>대형 수주 공시 임박 및 자사주 매수, 외인 매수세 언급하며 상승 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['신용 물량', '반도체 침체', '52주 최저가']</t>
+          <t>['대형 수주', '자사주', '외인 매수']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,97 +1016,189 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>빅텍</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3535</v>
+        <v>58900</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-7.22%</t>
+          <t>'-0.84%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="E7" t="n">
-        <v>121</v>
+        <v>67</v>
       </c>
       <c r="F7" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="G7" t="n">
-        <v>169</v>
+        <v>203</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>22.23</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3810</v>
+        <v>59400</v>
       </c>
       <c r="K7" t="n">
-        <v>3250</v>
+        <v>58300</v>
       </c>
       <c r="L7" t="n">
-        <v>3545</v>
+        <v>59100</v>
       </c>
       <c r="M7" t="n">
-        <v>3215</v>
+        <v>57600</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>22.25</v>
       </c>
       <c r="O7" t="n">
-        <v>9198464666</v>
+        <v>18318344250</v>
       </c>
       <c r="P7" t="n">
-        <v>7050</v>
+        <v>139200</v>
       </c>
       <c r="Q7" t="n">
-        <v>2500</v>
+        <v>57000</v>
       </c>
       <c r="R7" t="n">
-        <v>141000</v>
+        <v>37000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>북한의 자주포 남쪽 조준 및 미-이란 전면전 위기 고조와 관련된 군사적 긴장감 속에서 일부 기대감 형성. 그러나 변동성이 큰 양상.</t>
+          <t>신용 물량, IMF, 정치적 요인 언급하며 급락 및 부진한 주가 흐름에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['신용', 'IMF', '정치']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>빅텍</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3530</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>'-7.35%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>143</v>
+      </c>
+      <c r="F8" t="n">
+        <v>88</v>
+      </c>
+      <c r="G8" t="n">
+        <v>187</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>3810</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3250</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3555</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3215</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>10716384359</v>
+      </c>
+      <c r="P8" t="n">
+        <v>7050</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="R8" t="n">
+        <v>141000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>북한 자주포 도발 및 미-이란 위기 고조 속 하락 및 변동성 언급.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
         <v>0.2</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>['군사적 긴장', '자주포', '전면전 위기']</t>
-        </is>
-      </c>
-      <c r="X7" t="n">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['자주포', '위기', '변동성']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
         <v>5</v>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>065450</t>
         </is>

--- a/data/trending_integrated_20261026_09.xlsx
+++ b/data/trending_integrated_20261026_09.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14440</v>
+        <v>14690</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+27.79%</t>
+          <t>'+30.00%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F2" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G2" t="n">
-        <v>134</v>
+        <v>183</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>39027837240</v>
+        <v>42103359150</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>글로벌 AI 신약 밸류체인 합류, 빅파마와 후기 임상 진입, 美 서밋과 항암 신약 개발 협력 등 다수 호재 기반 급등.</t>
+          <t>AI 신약 개발 관련 빅파마 협력 및 밸류체인 합류로 인한 급등 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI 신약', '후기 임상', '항암 신약']</t>
+          <t>['AI 신약', '빅파마 협력', '밸류체인']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5800</v>
+        <v>5780</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+5.65%</t>
+          <t>'+5.28%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F3" t="n">
         <v>19</v>
       </c>
       <c r="G3" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -702,7 +702,7 @@
         <v>2.67</v>
       </c>
       <c r="O3" t="n">
-        <v>12420970510</v>
+        <v>12801185535</v>
       </c>
       <c r="P3" t="n">
         <v>7400</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정치 테마 관련 부정적 언급 및 급락 전망.</t>
+          <t>정치 테마주로 분류되어 실체가 없다는 주장과 함께 급락 예상.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['정치 테마', '급락', '사기']</t>
+          <t>['정치 테마주', '실체 없음', '급락']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1293000</v>
+        <v>1284000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.25%</t>
+          <t>'+0.55%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.08</v>
       </c>
       <c r="E4" t="n">
-        <v>777</v>
+        <v>798</v>
       </c>
       <c r="F4" t="n">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="G4" t="n">
-        <v>2777</v>
+        <v>2840</v>
       </c>
       <c r="H4" t="n">
         <v>48.69</v>
@@ -794,7 +794,7 @@
         <v>48.77</v>
       </c>
       <c r="O4" t="n">
-        <v>760053997500</v>
+        <v>851086993500</v>
       </c>
       <c r="P4" t="n">
         <v>2987000</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>214250</v>
+        <v>213750</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-0.58%</t>
+          <t>'-0.81%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>641</v>
+        <v>659</v>
       </c>
       <c r="F5" t="n">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="G5" t="n">
-        <v>1684</v>
+        <v>1703</v>
       </c>
       <c r="H5" t="n">
         <v>46.11</v>
@@ -886,7 +886,7 @@
         <v>46.13</v>
       </c>
       <c r="O5" t="n">
-        <v>610813360000</v>
+        <v>680847085000</v>
       </c>
       <c r="P5" t="n">
         <v>374500</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59300</v>
+        <v>58400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.84%</t>
+          <t>'-1.68%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.49</v>
+        <v>-0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>268</v>
+        <v>206</v>
       </c>
       <c r="H6" t="n">
-        <v>40.39</v>
+        <v>22.23</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>59800</v>
+        <v>59400</v>
       </c>
       <c r="K6" t="n">
-        <v>59400</v>
+        <v>58300</v>
       </c>
       <c r="L6" t="n">
-        <v>60200</v>
+        <v>59100</v>
       </c>
       <c r="M6" t="n">
-        <v>57800</v>
+        <v>57600</v>
       </c>
       <c r="N6" t="n">
-        <v>38.9</v>
+        <v>22.25</v>
       </c>
       <c r="O6" t="n">
-        <v>80859314650</v>
+        <v>20588949700</v>
       </c>
       <c r="P6" t="n">
-        <v>67300</v>
+        <v>139200</v>
       </c>
       <c r="Q6" t="n">
-        <v>23150</v>
+        <v>57000</v>
       </c>
       <c r="R6" t="n">
-        <v>85000</v>
+        <v>37000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>대형 수주 공시 임박 및 자사주 매수, 외인 매수세 언급하며 상승 기대.</t>
+          <t>신용 물량, IMF, 정치적 요인 언급하며 급락 및 부진한 주가 흐름에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['대형 수주', '자사주', '외인 매수']</t>
+          <t>['신용', 'IMF', '정치']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58900</v>
+        <v>58700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.84%</t>
+          <t>'-1.84%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.02</v>
+        <v>1.49</v>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F7" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="G7" t="n">
-        <v>203</v>
+        <v>301</v>
       </c>
       <c r="H7" t="n">
-        <v>22.23</v>
+        <v>40.39</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
+        <v>59800</v>
+      </c>
+      <c r="K7" t="n">
         <v>59400</v>
       </c>
-      <c r="K7" t="n">
-        <v>58300</v>
-      </c>
       <c r="L7" t="n">
-        <v>59100</v>
+        <v>60200</v>
       </c>
       <c r="M7" t="n">
-        <v>57600</v>
+        <v>57800</v>
       </c>
       <c r="N7" t="n">
-        <v>22.25</v>
+        <v>38.9</v>
       </c>
       <c r="O7" t="n">
-        <v>18318344250</v>
+        <v>90066941350</v>
       </c>
       <c r="P7" t="n">
-        <v>139200</v>
+        <v>67300</v>
       </c>
       <c r="Q7" t="n">
-        <v>57000</v>
+        <v>23150</v>
       </c>
       <c r="R7" t="n">
-        <v>37000</v>
+        <v>85000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>신용 물량, IMF, 정치적 요인 언급하며 급락 및 부진한 주가 흐름에 대한 부정적 전망.</t>
+          <t>대형 수주 공시 임박 및 자사주 매수 호재 기반 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['신용', 'IMF', '정치']</t>
+          <t>['대형 수주', '공시 임박', '자사주 매수']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3530</v>
+        <v>3440</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-7.35%</t>
+          <t>'-9.71%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F8" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G8" t="n">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>10716384359</v>
+        <v>11895263601</v>
       </c>
       <c r="P8" t="n">
         <v>7050</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>북한 자주포 도발 및 미-이란 위기 고조 속 하락 및 변동성 언급.</t>
+          <t>북한 군사 도발 및 미중 갈등 고조로 인한 변동성 확대, 하락세.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['자주포', '위기', '변동성']</t>
+          <t>['북한 도발', '미중 갈등', '변동성']</t>
         </is>
       </c>
       <c r="X8" t="n">

--- a/data/trending_integrated_20261026_09.xlsx
+++ b/data/trending_integrated_20261026_09.xlsx
@@ -578,13 +578,13 @@
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="F2" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G2" t="n">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>42103359150</v>
+        <v>42350856270</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 신약 개발 관련 빅파마 협력 및 밸류체인 합류로 인한 급등 전망.</t>
+          <t>AI 신약 밸류체인 합류 및 빅파마와 후기 임상 진입 뉴스 확인. 글로벌 협력 확대 및 주가 급등 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI 신약', '빅파마 협력', '밸류체인']</t>
+          <t>['AI 신약', '글로벌 협력', '임상 진입']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5780</v>
+        <v>5630</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+5.28%</t>
+          <t>'+2.55%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G3" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -696,13 +696,13 @@
         <v>6340</v>
       </c>
       <c r="M3" t="n">
-        <v>5650</v>
+        <v>5630</v>
       </c>
       <c r="N3" t="n">
         <v>2.67</v>
       </c>
       <c r="O3" t="n">
-        <v>12801185535</v>
+        <v>13379322645</v>
       </c>
       <c r="P3" t="n">
         <v>7400</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정치 테마주로 분류되어 실체가 없다는 주장과 함께 급락 예상.</t>
+          <t>정치 테마주로 분류되며, 특정 정치인 지지율과 연관된 부정적 전망. 주가 하락 및 퇴출 경고.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['정치 테마주', '실체 없음', '급락']</t>
+          <t>['정치 테마주', '주가 하락']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1284000</v>
+        <v>1285000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.55%</t>
+          <t>'+0.63%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.08</v>
       </c>
       <c r="E4" t="n">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="G4" t="n">
-        <v>2840</v>
+        <v>2495</v>
       </c>
       <c r="H4" t="n">
         <v>48.69</v>
@@ -794,7 +794,7 @@
         <v>48.77</v>
       </c>
       <c r="O4" t="n">
-        <v>851086993500</v>
+        <v>934025518500</v>
       </c>
       <c r="P4" t="n">
         <v>2987000</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>日 키옥시아 지분 차익 16조원 특별배당 추진 뉴스 기반 강한 상승 기대.</t>
+          <t>키옥시아 지분 차익 기반 16조원 특별배당 추진 뉴스 확인. 향후 실적 및 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['특별배당', '키옥시아', '지분 차익']</t>
+          <t>['특별배당', '키옥시아', '실적 전망']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>213750</v>
+        <v>213500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-0.81%</t>
+          <t>'-0.93%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>659</v>
+        <v>722</v>
       </c>
       <c r="F5" t="n">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="G5" t="n">
-        <v>1703</v>
+        <v>1781</v>
       </c>
       <c r="H5" t="n">
         <v>46.11</v>
@@ -886,7 +886,7 @@
         <v>46.13</v>
       </c>
       <c r="O5" t="n">
-        <v>680847085000</v>
+        <v>749641939500</v>
       </c>
       <c r="P5" t="n">
         <v>374500</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58400</v>
+        <v>58500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.68%</t>
+          <t>'-2.17%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.02</v>
+        <v>1.49</v>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F6" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G6" t="n">
-        <v>206</v>
+        <v>330</v>
       </c>
       <c r="H6" t="n">
-        <v>22.23</v>
+        <v>40.39</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
+        <v>59800</v>
+      </c>
+      <c r="K6" t="n">
         <v>59400</v>
       </c>
-      <c r="K6" t="n">
-        <v>58300</v>
-      </c>
       <c r="L6" t="n">
-        <v>59100</v>
+        <v>60200</v>
       </c>
       <c r="M6" t="n">
-        <v>57600</v>
+        <v>57800</v>
       </c>
       <c r="N6" t="n">
-        <v>22.25</v>
+        <v>38.9</v>
       </c>
       <c r="O6" t="n">
-        <v>20588949700</v>
+        <v>99886825350</v>
       </c>
       <c r="P6" t="n">
-        <v>139200</v>
+        <v>67300</v>
       </c>
       <c r="Q6" t="n">
-        <v>57000</v>
+        <v>23150</v>
       </c>
       <c r="R6" t="n">
-        <v>37000</v>
+        <v>85000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>신용 물량, IMF, 정치적 요인 언급하며 급락 및 부진한 주가 흐름에 대한 부정적 전망.</t>
+          <t>대형 수주 공시 임박 가능성과 자사주 매수를 기반으로 한 긍정적 전망. 공매도 세력에 대한 경고.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['신용', 'IMF', '정치']</t>
+          <t>['대형 수주', '자사주 매수', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58700</v>
+        <v>57900</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.84%</t>
+          <t>'-2.53%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.49</v>
+        <v>-0.02</v>
       </c>
       <c r="E7" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="F7" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="G7" t="n">
-        <v>301</v>
+        <v>220</v>
       </c>
       <c r="H7" t="n">
-        <v>40.39</v>
+        <v>22.23</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>59800</v>
+        <v>59400</v>
       </c>
       <c r="K7" t="n">
-        <v>59400</v>
+        <v>58300</v>
       </c>
       <c r="L7" t="n">
-        <v>60200</v>
+        <v>59100</v>
       </c>
       <c r="M7" t="n">
-        <v>57800</v>
+        <v>57600</v>
       </c>
       <c r="N7" t="n">
-        <v>38.9</v>
+        <v>22.25</v>
       </c>
       <c r="O7" t="n">
-        <v>90066941350</v>
+        <v>22882063750</v>
       </c>
       <c r="P7" t="n">
-        <v>67300</v>
+        <v>139200</v>
       </c>
       <c r="Q7" t="n">
-        <v>23150</v>
+        <v>57000</v>
       </c>
       <c r="R7" t="n">
-        <v>85000</v>
+        <v>37000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>대형 수주 공시 임박 및 자사주 매수 호재 기반 주가 상승 기대.</t>
+          <t>현재 주가에 대한 강한 부정적 인식과 향후 추가 하락 가능성 제기. 실적 부진 및 정치적 이슈 연관성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['대형 수주', '공시 임박', '자사주 매수']</t>
+          <t>['실적 부진', '주가 하락', '신용 매물']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3440</v>
+        <v>3365</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-9.71%</t>
+          <t>'-11.68%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="F8" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G8" t="n">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>11895263601</v>
+        <v>13110077805</v>
       </c>
       <c r="P8" t="n">
         <v>7050</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>북한 군사 도발 및 미중 갈등 고조로 인한 변동성 확대, 하락세.</t>
+          <t>북한 군사 도발 관련 지정학적 리스크 부각. 주가 하락세 속에서 외국인 매수 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['북한 도발', '미중 갈등', '변동성']</t>
+          <t>['지정학적 리스크', '북한 도발', '외국인 매수']</t>
         </is>
       </c>
       <c r="X8" t="n">
